--- a/02_加值成品/歷屆試題/110年會考自然科.xlsx
+++ b/02_加值成品/歷屆試題/110年會考自然科.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>依慣性定律，乘客會維持原有運動狀態：車子急左轉時，乘客身體會因慣性往右側甩；車子急加速時，乘客身體會因慣性相對往後(車後方)傾。需依圖中歹徒身體被甩動的方向，判斷對應的操控方式為先急左轉再急加速。</t>
+          <t>依慣性定律，乘客的身體傾向維持原本的運動狀態。車子向左急轉時，乘客因慣性繼續朝原方向前進，相對車廂而言身體會被甩向右側；此時再配合圖(六)中歹徒身體被甩動的實際方向判讀，官方答案判定對應的操控方式為「先急左轉再急加速」。此題須配合原題圖(六)的路線與甩動方向才能完整確認，建議對照圖片。</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>電解硫酸銅時，陽極(接電源正極)發生氧化反應。若陽極為惰性電極(碳棒)，則水被氧化產生氧氣；若陽極為銅棒(活性電極)，則是銅本身溶解成銅離子而不產生氧氣。故僅在碳棒作為陽極的那一支電極附近會產生氧氣，需依圖中導線接法判斷該電極。</t>
+          <t>電解硫酸銅時，陽極(接電源正極)發生氧化反應。銅棒(丙、丁)不論是陽極還是陰極都不會產生氧氣：當陽極是銅棒時，是銅本身溶解成銅離子，不是水被氧化；所以答案一定是碳棒甲或碳棒乙其中之一，先排除C、D。接著要看圖(十四)、(十五)中紅色導線實際接的是電源正極還是負極，才能判斷碳棒甲、乙誰是陽極——這一步需要對照原題圖片，官方答案為碳棒乙。</t>
         </is>
       </c>
     </row>
